--- a/Experimenten6.xlsx
+++ b/Experimenten6.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stichtingfontys-my.sharepoint.com/personal/582755_student_fontys_nl/Documents/Leerjaar 2/Periode 1/Operations Research 5/OR5/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="11_CFD6CF5F49E78B6A9AACDF9691120D542D00B0A3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DBDFF003-6F35-4CA9-AF8D-C12E1AC4EC16}"/>
+  <xr:revisionPtr revIDLastSave="34" documentId="11_86E68E5B49478F1E915F0D70EBA24D1510A2682F" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D070B6F-2040-4AD8-A810-DE83C360E611}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="2130" yWindow="2130" windowWidth="17280" windowHeight="8925" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Alle experimenten" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="16">
   <si>
     <t>t_max</t>
   </si>
@@ -84,17 +84,14 @@
   <si>
     <t>Aantal_runs</t>
   </si>
-  <si>
-    <t>gem van gem</t>
-  </si>
-  <si>
-    <t>gem van std</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -124,8 +121,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -141,6 +139,1270 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Gemiddelde totale penalty per cooling</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> iteratie</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Samenvatting!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Gemiddelde_penalty</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{06E10E8D-4905-4D72-9048-F1C25B8907EE}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="nl-NL"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000002-362F-4612-843B-E96E454B3D38}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{39E1F644-E330-4486-A77A-1A941AC89E10}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="nl-NL"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-362F-4612-843B-E96E454B3D38}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{F7F0892E-6D85-4903-B3FB-CA5B5672F520}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="nl-NL"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000004-362F-4612-843B-E96E454B3D38}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{DE5B14F5-3037-492B-87C5-32A049EBDCBE}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="nl-NL"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000005-362F-4612-843B-E96E454B3D38}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="nl-NL"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showDataLabelsRange val="1"/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:numRef>
+              <c:f>Samenvatting!$B$2:$B$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>700</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1400</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Samenvatting!$C$2:$C$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>300.27777777777771</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>332.04444444444442</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>314.80555555555549</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>344.75555555555547</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+              <c15:datalabelsRange>
+                <c15:f>Samenvatting!$E$2:$E$5</c15:f>
+                <c15:dlblRangeCache>
+                  <c:ptCount val="4"/>
+                  <c:pt idx="0">
+                    <c:v>59,2</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>46,3</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>97,1</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>35,0</c:v>
+                  </c:pt>
+                </c15:dlblRangeCache>
+              </c15:datalabelsRange>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-362F-4612-843B-E96E454B3D38}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="405793584"/>
+        <c:axId val="417662384"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="405793584"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="nl-NL" sz="1200"/>
+                  <a:t>Cooling iteratie</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="nl-NL"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="nl-NL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="417662384"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="417662384"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="nl-NL" sz="1200"/>
+                  <a:t>Gemiddelde penalty</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="1.4383058572905946E-2"/>
+              <c:y val="0.34129996426345599"/>
+            </c:manualLayout>
+          </c:layout>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="nl-NL"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="nl-NL"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="405793584"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="nl-NL"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="nl-NL"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>76199</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>33337</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2B136CB1-B181-337B-BF09-C8FF775D658F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -428,7 +1690,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.42578125" bestFit="1" customWidth="1"/>
@@ -490,28 +1752,28 @@
         <v>700</v>
       </c>
       <c r="D2">
-        <v>750</v>
+        <v>500</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2">
-        <v>258.44444444444451</v>
+        <v>373.36111111111097</v>
       </c>
       <c r="G2">
-        <v>258.44444444444451</v>
+        <v>373.36111111111097</v>
       </c>
       <c r="H2">
-        <v>37.666666666666657</v>
+        <v>53.138888888888879</v>
       </c>
       <c r="I2">
-        <v>6.123147100006463</v>
+        <v>4.4048998000071151</v>
       </c>
       <c r="J2">
-        <v>2.3428600004990589E-2</v>
+        <v>2.143530000466853E-2</v>
       </c>
       <c r="K2">
-        <v>6.1465757000114536</v>
+        <v>4.4263351000117837</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -525,28 +1787,28 @@
         <v>700</v>
       </c>
       <c r="D3">
-        <v>750</v>
+        <v>500</v>
       </c>
       <c r="E3">
         <v>9</v>
       </c>
       <c r="F3">
-        <v>358.66666666666703</v>
+        <v>273.44444444444429</v>
       </c>
       <c r="G3">
-        <v>351.16666666666669</v>
+        <v>273.44444444444429</v>
       </c>
       <c r="H3">
-        <v>51.916666666666671</v>
+        <v>40.527777777777757</v>
       </c>
       <c r="I3">
-        <v>4.606510800003889</v>
+        <v>4.4127573000005214</v>
       </c>
       <c r="J3">
-        <v>4.5312899994314648E-2</v>
+        <v>2.917199999501463E-2</v>
       </c>
       <c r="K3">
-        <v>4.6518236999982037</v>
+        <v>4.441929299995536</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -560,28 +1822,28 @@
         <v>700</v>
       </c>
       <c r="D4">
-        <v>750</v>
+        <v>500</v>
       </c>
       <c r="E4">
         <v>14</v>
       </c>
       <c r="F4">
-        <v>387.83333333333343</v>
+        <v>267.94444444444451</v>
       </c>
       <c r="G4">
-        <v>387.83333333333343</v>
+        <v>267.94444444444451</v>
       </c>
       <c r="H4">
-        <v>53.5</v>
+        <v>40.027777777777779</v>
       </c>
       <c r="I4">
-        <v>4.4082492000015918</v>
+        <v>4.3625010999967344</v>
       </c>
       <c r="J4">
-        <v>2.6228499991702851E-2</v>
+        <v>2.319469999929424E-2</v>
       </c>
       <c r="K4">
-        <v>4.4344776999932947</v>
+        <v>4.3856957999960287</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -595,28 +1857,28 @@
         <v>700</v>
       </c>
       <c r="D5">
-        <v>750</v>
+        <v>500</v>
       </c>
       <c r="E5">
         <v>32</v>
       </c>
       <c r="F5">
-        <v>319.83333333333343</v>
+        <v>235</v>
       </c>
       <c r="G5">
-        <v>319.83333333333343</v>
+        <v>235</v>
       </c>
       <c r="H5">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="I5">
-        <v>4.4747035000036703</v>
+        <v>4.206734300008975</v>
       </c>
       <c r="J5">
-        <v>2.5713099996210079E-2</v>
+        <v>2.1747299993876371E-2</v>
       </c>
       <c r="K5">
-        <v>4.5004165999998804</v>
+        <v>4.2284816000028513</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -630,28 +1892,28 @@
         <v>700</v>
       </c>
       <c r="D6">
-        <v>750</v>
+        <v>500</v>
       </c>
       <c r="E6">
         <v>88</v>
       </c>
       <c r="F6">
-        <v>343.16666666666657</v>
+        <v>351.6388888888888</v>
       </c>
       <c r="G6">
-        <v>343.16666666666657</v>
+        <v>351.6388888888888</v>
       </c>
       <c r="H6">
-        <v>50.694444444444443</v>
+        <v>49.222222222222207</v>
       </c>
       <c r="I6">
-        <v>4.4511911000008686</v>
+        <v>4.164658399997279</v>
       </c>
       <c r="J6">
-        <v>2.8189099990413521E-2</v>
+        <v>2.2211699993931688E-2</v>
       </c>
       <c r="K6">
-        <v>4.479380199991283</v>
+        <v>4.1868700999912107</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -665,28 +1927,28 @@
         <v>1000</v>
       </c>
       <c r="D7">
-        <v>750</v>
+        <v>500</v>
       </c>
       <c r="E7">
         <v>1</v>
       </c>
       <c r="F7">
-        <v>220.5</v>
+        <v>376.08333333333309</v>
       </c>
       <c r="G7">
-        <v>220.5</v>
+        <v>376.08333333333309</v>
       </c>
       <c r="H7">
-        <v>36.5</v>
+        <v>58.666666666666643</v>
       </c>
       <c r="I7">
-        <v>4.5015864000015426</v>
+        <v>4.2270635999884689</v>
       </c>
       <c r="J7">
-        <v>2.31426999962423E-2</v>
+        <v>2.2574500006157901E-2</v>
       </c>
       <c r="K7">
-        <v>4.5247290999977849</v>
+        <v>4.2496380999946268</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -700,28 +1962,28 @@
         <v>1000</v>
       </c>
       <c r="D8">
-        <v>750</v>
+        <v>500</v>
       </c>
       <c r="E8">
         <v>9</v>
       </c>
       <c r="F8">
-        <v>497.11111111111097</v>
+        <v>355.94444444444429</v>
       </c>
       <c r="G8">
-        <v>457.5555555555556</v>
+        <v>355.94444444444429</v>
       </c>
       <c r="H8">
-        <v>54.972222222222221</v>
+        <v>52.833333333333307</v>
       </c>
       <c r="I8">
-        <v>4.4623992999986513</v>
+        <v>4.2444137999991653</v>
       </c>
       <c r="J8">
-        <v>0.11325480000232351</v>
+        <v>2.2965100011788309E-2</v>
       </c>
       <c r="K8">
-        <v>4.5756541000009747</v>
+        <v>4.2673789000109537</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -735,28 +1997,28 @@
         <v>1000</v>
       </c>
       <c r="D9">
-        <v>750</v>
+        <v>500</v>
       </c>
       <c r="E9">
         <v>14</v>
       </c>
       <c r="F9">
-        <v>629.16666666666697</v>
+        <v>262.72222222222229</v>
       </c>
       <c r="G9">
-        <v>620.83333333333348</v>
+        <v>262.72222222222229</v>
       </c>
       <c r="H9">
-        <v>82.250000000000014</v>
+        <v>39.027777777777793</v>
       </c>
       <c r="I9">
-        <v>4.5179561000113608</v>
+        <v>4.3653252000076463</v>
       </c>
       <c r="J9">
-        <v>4.7168400007649318E-2</v>
+        <v>9.0760899998713285E-2</v>
       </c>
       <c r="K9">
-        <v>4.5651245000190102</v>
+        <v>4.4560861000063596</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -770,28 +2032,28 @@
         <v>1000</v>
       </c>
       <c r="D10">
-        <v>750</v>
+        <v>500</v>
       </c>
       <c r="E10">
         <v>32</v>
       </c>
       <c r="F10">
-        <v>340.8888888888888</v>
+        <v>357.91666666666669</v>
       </c>
       <c r="G10">
-        <v>340.8888888888888</v>
+        <v>357.91666666666669</v>
       </c>
       <c r="H10">
-        <v>51.277777777777757</v>
+        <v>41.027777777777779</v>
       </c>
       <c r="I10">
-        <v>4.4703731999907177</v>
+        <v>4.9658936000050744</v>
       </c>
       <c r="J10">
-        <v>2.4671799998031929E-2</v>
+        <v>2.4404900002991781E-2</v>
       </c>
       <c r="K10">
-        <v>4.4950449999887496</v>
+        <v>4.9902985000080662</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -805,28 +2067,28 @@
         <v>1000</v>
       </c>
       <c r="D11">
-        <v>750</v>
+        <v>500</v>
       </c>
       <c r="E11">
         <v>88</v>
       </c>
       <c r="F11">
-        <v>326.47222222222229</v>
+        <v>307.55555555555549</v>
       </c>
       <c r="G11">
-        <v>275.66666666666669</v>
+        <v>307.55555555555549</v>
       </c>
       <c r="H11">
-        <v>36.722222222222229</v>
+        <v>42.694444444444443</v>
       </c>
       <c r="I11">
-        <v>4.5117427999939537</v>
+        <v>4.8923033000028227</v>
       </c>
       <c r="J11">
-        <v>0.13856619999569381</v>
+        <v>2.8147300006821752E-2</v>
       </c>
       <c r="K11">
-        <v>4.6503089999896474</v>
+        <v>4.9204506000096444</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -840,28 +2102,28 @@
         <v>1400</v>
       </c>
       <c r="D12">
-        <v>750</v>
+        <v>500</v>
       </c>
       <c r="E12">
         <v>1</v>
       </c>
       <c r="F12">
-        <v>305.44444444444429</v>
+        <v>321.27777777777783</v>
       </c>
       <c r="G12">
-        <v>296.5555555555552</v>
+        <v>321.27777777777783</v>
       </c>
       <c r="H12">
-        <v>41.416666666666643</v>
+        <v>50.583333333333343</v>
       </c>
       <c r="I12">
-        <v>4.7090103000082308</v>
+        <v>4.8801423999975668</v>
       </c>
       <c r="J12">
-        <v>6.9234400012646802E-2</v>
+        <v>2.6661500000045631E-2</v>
       </c>
       <c r="K12">
-        <v>4.7782447000208776</v>
+        <v>4.9068038999976116</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -875,28 +2137,28 @@
         <v>1400</v>
       </c>
       <c r="D13">
-        <v>750</v>
+        <v>500</v>
       </c>
       <c r="E13">
         <v>9</v>
       </c>
       <c r="F13">
-        <v>421.88888888888891</v>
+        <v>316.11111111111109</v>
       </c>
       <c r="G13">
-        <v>407.33333333333331</v>
+        <v>316.11111111111109</v>
       </c>
       <c r="H13">
-        <v>54.05555555555555</v>
+        <v>42.722222222222207</v>
       </c>
       <c r="I13">
-        <v>4.6134663000120781</v>
+        <v>5.5218110999994678</v>
       </c>
       <c r="J13">
-        <v>6.9288800004869699E-2</v>
+        <v>2.7208899991819639E-2</v>
       </c>
       <c r="K13">
-        <v>4.6827551000169478</v>
+        <v>5.5490199999912866</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -910,28 +2172,28 @@
         <v>1400</v>
       </c>
       <c r="D14">
-        <v>750</v>
+        <v>500</v>
       </c>
       <c r="E14">
         <v>14</v>
       </c>
       <c r="F14">
-        <v>310.61111111111109</v>
+        <v>363.36111111111069</v>
       </c>
       <c r="G14">
-        <v>310.61111111111109</v>
+        <v>363.36111111111069</v>
       </c>
       <c r="H14">
-        <v>40.777777777777771</v>
+        <v>42.083333333333293</v>
       </c>
       <c r="I14">
-        <v>4.5249672000063583</v>
+        <v>4.984524200001033</v>
       </c>
       <c r="J14">
-        <v>2.5157900003250688E-2</v>
+        <v>3.2019599995692261E-2</v>
       </c>
       <c r="K14">
-        <v>4.550125100009609</v>
+        <v>5.0165437999967253</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -945,28 +2207,28 @@
         <v>1400</v>
       </c>
       <c r="D15">
-        <v>750</v>
+        <v>500</v>
       </c>
       <c r="E15">
         <v>32</v>
       </c>
       <c r="F15">
-        <v>518.63888888888903</v>
+        <v>416.50000000000011</v>
       </c>
       <c r="G15">
-        <v>492.13888888888903</v>
+        <v>416.50000000000011</v>
       </c>
       <c r="H15">
-        <v>66.944444444444457</v>
+        <v>57.027777777777793</v>
       </c>
       <c r="I15">
-        <v>4.4858758000045782</v>
+        <v>5.2784501999994973</v>
       </c>
       <c r="J15">
-        <v>7.1591899992199615E-2</v>
+        <v>2.4812299991026521E-2</v>
       </c>
       <c r="K15">
-        <v>4.5574676999967778</v>
+        <v>5.3032624999905238</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -980,28 +2242,28 @@
         <v>1400</v>
       </c>
       <c r="D16">
-        <v>750</v>
+        <v>500</v>
       </c>
       <c r="E16">
         <v>88</v>
       </c>
       <c r="F16">
-        <v>306.24999999999977</v>
+        <v>156.77777777777769</v>
       </c>
       <c r="G16">
-        <v>306.24999999999977</v>
+        <v>156.77777777777769</v>
       </c>
       <c r="H16">
-        <v>46.888888888888857</v>
+        <v>18.833333333333329</v>
       </c>
       <c r="I16">
-        <v>4.974801500007743</v>
+        <v>4.7564500000007683</v>
       </c>
       <c r="J16">
-        <v>2.8121899988036599E-2</v>
+        <v>2.3803900010534559E-2</v>
       </c>
       <c r="K16">
-        <v>5.0029233999957796</v>
+        <v>4.7802539000113029</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -1015,28 +2277,28 @@
         <v>7000</v>
       </c>
       <c r="D17">
-        <v>750</v>
+        <v>500</v>
       </c>
       <c r="E17">
         <v>1</v>
       </c>
       <c r="F17">
-        <v>331.38888888888908</v>
+        <v>393.27777777777771</v>
       </c>
       <c r="G17">
-        <v>331.38888888888908</v>
+        <v>393.27777777777771</v>
       </c>
       <c r="H17">
-        <v>43.055555555555571</v>
+        <v>57.833333333333329</v>
       </c>
       <c r="I17">
-        <v>4.7042307999945479</v>
+        <v>4.6513180999900214</v>
       </c>
       <c r="J17">
-        <v>2.5518599999486469E-2</v>
+        <v>2.6022500009275969E-2</v>
       </c>
       <c r="K17">
-        <v>4.7297493999940343</v>
+        <v>4.6773405999992974</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
@@ -1050,28 +2312,28 @@
         <v>7000</v>
       </c>
       <c r="D18">
-        <v>750</v>
+        <v>500</v>
       </c>
       <c r="E18">
         <v>9</v>
       </c>
       <c r="F18">
-        <v>249.61111111111131</v>
+        <v>362.49999999999989</v>
       </c>
       <c r="G18">
-        <v>249.61111111111131</v>
+        <v>362.49999999999989</v>
       </c>
       <c r="H18">
-        <v>37.222222222222243</v>
+        <v>54.249999999999993</v>
       </c>
       <c r="I18">
-        <v>4.5586198999953922</v>
+        <v>4.7809929999930318</v>
       </c>
       <c r="J18">
-        <v>2.2771899995859709E-2</v>
+        <v>2.5980200007325038E-2</v>
       </c>
       <c r="K18">
-        <v>4.5813917999912519</v>
+        <v>4.8069732000003569</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
@@ -1085,28 +2347,28 @@
         <v>7000</v>
       </c>
       <c r="D19">
-        <v>750</v>
+        <v>500</v>
       </c>
       <c r="E19">
         <v>14</v>
       </c>
       <c r="F19">
-        <v>556.88888888888891</v>
+        <v>349.41666666666652</v>
       </c>
       <c r="G19">
-        <v>556.88888888888891</v>
+        <v>310.41666666666657</v>
       </c>
       <c r="H19">
-        <v>79.222222222222214</v>
+        <v>46.916666666666657</v>
       </c>
       <c r="I19">
-        <v>4.6303005000081612</v>
+        <v>4.8326491000043461</v>
       </c>
       <c r="J19">
-        <v>2.4192099997890178E-2</v>
+        <v>7.5822000013431534E-2</v>
       </c>
       <c r="K19">
-        <v>4.6544926000060514</v>
+        <v>4.9084711000177776</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -1120,28 +2382,28 @@
         <v>7000</v>
       </c>
       <c r="D20">
-        <v>750</v>
+        <v>500</v>
       </c>
       <c r="E20">
         <v>32</v>
       </c>
       <c r="F20">
-        <v>330.58333333333331</v>
+        <v>345.30555555555549</v>
       </c>
       <c r="G20">
-        <v>283.5</v>
+        <v>345.30555555555549</v>
       </c>
       <c r="H20">
-        <v>46.583333333333329</v>
+        <v>50.361111111111107</v>
       </c>
       <c r="I20">
-        <v>4.6111495000077412</v>
+        <v>5.441249900002731</v>
       </c>
       <c r="J20">
-        <v>6.9976099999621511E-2</v>
+        <v>3.3075899991672493E-2</v>
       </c>
       <c r="K20">
-        <v>4.6811256000073627</v>
+        <v>5.4743257999944026</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
@@ -1155,728 +2417,28 @@
         <v>7000</v>
       </c>
       <c r="D21">
-        <v>750</v>
+        <v>500</v>
       </c>
       <c r="E21">
         <v>88</v>
       </c>
       <c r="F21">
-        <v>326.83333333333297</v>
+        <v>312.2777777777776</v>
       </c>
       <c r="G21">
-        <v>326.83333333333297</v>
+        <v>312.2777777777776</v>
       </c>
       <c r="H21">
-        <v>50.527777777777743</v>
+        <v>47.166666666666643</v>
       </c>
       <c r="I21">
-        <v>4.5462439000111772</v>
+        <v>5.5131545999902301</v>
       </c>
       <c r="J21">
-        <v>2.307869998912793E-2</v>
+        <v>2.824759999930393E-2</v>
       </c>
       <c r="K21">
-        <v>4.5693226000003051</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>70000</v>
-      </c>
-      <c r="B22">
-        <v>0.954992586021436</v>
-      </c>
-      <c r="C22">
-        <v>700</v>
-      </c>
-      <c r="D22">
-        <v>1000</v>
-      </c>
-      <c r="E22">
-        <v>1</v>
-      </c>
-      <c r="F22">
-        <v>300.5</v>
-      </c>
-      <c r="G22">
-        <v>300.5</v>
-      </c>
-      <c r="H22">
-        <v>43.083333333333329</v>
-      </c>
-      <c r="I22">
-        <v>4.59514429999399</v>
-      </c>
-      <c r="J22">
-        <v>2.7057900006184351E-2</v>
-      </c>
-      <c r="K22">
-        <v>4.6222022000001743</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>70000</v>
-      </c>
-      <c r="B23">
-        <v>0.954992586021436</v>
-      </c>
-      <c r="C23">
-        <v>700</v>
-      </c>
-      <c r="D23">
-        <v>1000</v>
-      </c>
-      <c r="E23">
-        <v>9</v>
-      </c>
-      <c r="F23">
-        <v>248.83333333333329</v>
-      </c>
-      <c r="G23">
-        <v>248.83333333333329</v>
-      </c>
-      <c r="H23">
-        <v>36.888888888888893</v>
-      </c>
-      <c r="I23">
-        <v>4.6026233000011416</v>
-      </c>
-      <c r="J23">
-        <v>2.568069999688305E-2</v>
-      </c>
-      <c r="K23">
-        <v>4.6283039999980247</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>70000</v>
-      </c>
-      <c r="B24">
-        <v>0.954992586021436</v>
-      </c>
-      <c r="C24">
-        <v>700</v>
-      </c>
-      <c r="D24">
-        <v>1000</v>
-      </c>
-      <c r="E24">
-        <v>14</v>
-      </c>
-      <c r="F24">
-        <v>445.61111111111069</v>
-      </c>
-      <c r="G24">
-        <v>445.61111111111069</v>
-      </c>
-      <c r="H24">
-        <v>44.944444444444407</v>
-      </c>
-      <c r="I24">
-        <v>4.5953480000025593</v>
-      </c>
-      <c r="J24">
-        <v>2.448160000494681E-2</v>
-      </c>
-      <c r="K24">
-        <v>4.6198296000075061</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>70000</v>
-      </c>
-      <c r="B25">
-        <v>0.954992586021436</v>
-      </c>
-      <c r="C25">
-        <v>700</v>
-      </c>
-      <c r="D25">
-        <v>1000</v>
-      </c>
-      <c r="E25">
-        <v>32</v>
-      </c>
-      <c r="F25">
-        <v>383.74999999999989</v>
-      </c>
-      <c r="G25">
-        <v>370.75</v>
-      </c>
-      <c r="H25">
-        <v>51.75</v>
-      </c>
-      <c r="I25">
-        <v>4.5144277999934266</v>
-      </c>
-      <c r="J25">
-        <v>7.072360000165645E-2</v>
-      </c>
-      <c r="K25">
-        <v>4.5851513999950839</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>70000</v>
-      </c>
-      <c r="B26">
-        <v>0.954992586021436</v>
-      </c>
-      <c r="C26">
-        <v>700</v>
-      </c>
-      <c r="D26">
-        <v>1000</v>
-      </c>
-      <c r="E26">
-        <v>88</v>
-      </c>
-      <c r="F26">
-        <v>315.33333333333343</v>
-      </c>
-      <c r="G26">
-        <v>315.33333333333343</v>
-      </c>
-      <c r="H26">
-        <v>45.916666666666671</v>
-      </c>
-      <c r="I26">
-        <v>4.6814322999998694</v>
-      </c>
-      <c r="J26">
-        <v>2.5526500001433309E-2</v>
-      </c>
-      <c r="K26">
-        <v>4.7069588000013027</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>70000</v>
-      </c>
-      <c r="B27">
-        <v>0.93632920882394144</v>
-      </c>
-      <c r="C27">
-        <v>1000</v>
-      </c>
-      <c r="D27">
-        <v>1000</v>
-      </c>
-      <c r="E27">
-        <v>1</v>
-      </c>
-      <c r="F27">
-        <v>193</v>
-      </c>
-      <c r="G27">
-        <v>193</v>
-      </c>
-      <c r="H27">
-        <v>27.583333333333329</v>
-      </c>
-      <c r="I27">
-        <v>4.655333700007759</v>
-      </c>
-      <c r="J27">
-        <v>2.520479999657255E-2</v>
-      </c>
-      <c r="K27">
-        <v>4.6805385000043316</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28">
-        <v>70000</v>
-      </c>
-      <c r="B28">
-        <v>0.93632920882394144</v>
-      </c>
-      <c r="C28">
-        <v>1000</v>
-      </c>
-      <c r="D28">
-        <v>1000</v>
-      </c>
-      <c r="E28">
-        <v>9</v>
-      </c>
-      <c r="F28">
-        <v>301.27777777777749</v>
-      </c>
-      <c r="G28">
-        <v>301.27777777777749</v>
-      </c>
-      <c r="H28">
-        <v>42.4722222222222</v>
-      </c>
-      <c r="I28">
-        <v>4.6222531999956118</v>
-      </c>
-      <c r="J28">
-        <v>2.6131699996767569E-2</v>
-      </c>
-      <c r="K28">
-        <v>4.6483848999923794</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29">
-        <v>70000</v>
-      </c>
-      <c r="B29">
-        <v>0.93632920882394144</v>
-      </c>
-      <c r="C29">
-        <v>1000</v>
-      </c>
-      <c r="D29">
-        <v>1000</v>
-      </c>
-      <c r="E29">
-        <v>14</v>
-      </c>
-      <c r="F29">
-        <v>439.58333333333309</v>
-      </c>
-      <c r="G29">
-        <v>439.58333333333309</v>
-      </c>
-      <c r="H29">
-        <v>60.361111111111093</v>
-      </c>
-      <c r="I29">
-        <v>4.8129474000015762</v>
-      </c>
-      <c r="J29">
-        <v>2.4929599996539761E-2</v>
-      </c>
-      <c r="K29">
-        <v>4.8378769999981159</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>70000</v>
-      </c>
-      <c r="B30">
-        <v>0.93632920882394144</v>
-      </c>
-      <c r="C30">
-        <v>1000</v>
-      </c>
-      <c r="D30">
-        <v>1000</v>
-      </c>
-      <c r="E30">
-        <v>32</v>
-      </c>
-      <c r="F30">
-        <v>244.5555555555556</v>
-      </c>
-      <c r="G30">
-        <v>244.5555555555556</v>
-      </c>
-      <c r="H30">
-        <v>40.3888888888889</v>
-      </c>
-      <c r="I30">
-        <v>4.5563018999964697</v>
-      </c>
-      <c r="J30">
-        <v>2.5247600002330731E-2</v>
-      </c>
-      <c r="K30">
-        <v>4.5815494999987996</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31">
-        <v>70000</v>
-      </c>
-      <c r="B31">
-        <v>0.93632920882394144</v>
-      </c>
-      <c r="C31">
-        <v>1000</v>
-      </c>
-      <c r="D31">
-        <v>1000</v>
-      </c>
-      <c r="E31">
-        <v>88</v>
-      </c>
-      <c r="F31">
-        <v>305.38888888888903</v>
-      </c>
-      <c r="G31">
-        <v>305.38888888888903</v>
-      </c>
-      <c r="H31">
-        <v>46.611111111111107</v>
-      </c>
-      <c r="I31">
-        <v>4.6079448000091361</v>
-      </c>
-      <c r="J31">
-        <v>2.3168200001236979E-2</v>
-      </c>
-      <c r="K31">
-        <v>4.6311130000103731</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>70000</v>
-      </c>
-      <c r="B32">
-        <v>0.91201083935590976</v>
-      </c>
-      <c r="C32">
-        <v>1400</v>
-      </c>
-      <c r="D32">
-        <v>1000</v>
-      </c>
-      <c r="E32">
-        <v>1</v>
-      </c>
-      <c r="F32">
-        <v>304.47222222222217</v>
-      </c>
-      <c r="G32">
-        <v>304.47222222222217</v>
-      </c>
-      <c r="H32">
-        <v>40.6111111111111</v>
-      </c>
-      <c r="I32">
-        <v>4.6508086999965599</v>
-      </c>
-      <c r="J32">
-        <v>2.7202099998248741E-2</v>
-      </c>
-      <c r="K32">
-        <v>4.6780107999948086</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>70000</v>
-      </c>
-      <c r="B33">
-        <v>0.91201083935590976</v>
-      </c>
-      <c r="C33">
-        <v>1400</v>
-      </c>
-      <c r="D33">
-        <v>1000</v>
-      </c>
-      <c r="E33">
-        <v>9</v>
-      </c>
-      <c r="F33">
-        <v>218</v>
-      </c>
-      <c r="G33">
-        <v>218</v>
-      </c>
-      <c r="H33">
-        <v>24.583333333333329</v>
-      </c>
-      <c r="I33">
-        <v>4.6406711000017822</v>
-      </c>
-      <c r="J33">
-        <v>2.3629499992239289E-2</v>
-      </c>
-      <c r="K33">
-        <v>4.6643005999940206</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>70000</v>
-      </c>
-      <c r="B34">
-        <v>0.91201083935590976</v>
-      </c>
-      <c r="C34">
-        <v>1400</v>
-      </c>
-      <c r="D34">
-        <v>1000</v>
-      </c>
-      <c r="E34">
-        <v>14</v>
-      </c>
-      <c r="F34">
-        <v>304.5</v>
-      </c>
-      <c r="G34">
-        <v>304.5</v>
-      </c>
-      <c r="H34">
-        <v>46.166666666666657</v>
-      </c>
-      <c r="I34">
-        <v>4.5806421999877784</v>
-      </c>
-      <c r="J34">
-        <v>2.4520300008589398E-2</v>
-      </c>
-      <c r="K34">
-        <v>4.6051624999963678</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>70000</v>
-      </c>
-      <c r="B35">
-        <v>0.91201083935590976</v>
-      </c>
-      <c r="C35">
-        <v>1400</v>
-      </c>
-      <c r="D35">
-        <v>1000</v>
-      </c>
-      <c r="E35">
-        <v>32</v>
-      </c>
-      <c r="F35">
-        <v>526.2777777777776</v>
-      </c>
-      <c r="G35">
-        <v>511.77777777777783</v>
-      </c>
-      <c r="H35">
-        <v>52.055555555555557</v>
-      </c>
-      <c r="I35">
-        <v>4.5814150999940466</v>
-      </c>
-      <c r="J35">
-        <v>4.8647799994796508E-2</v>
-      </c>
-      <c r="K35">
-        <v>4.6300628999888431</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A36">
-        <v>70000</v>
-      </c>
-      <c r="B36">
-        <v>0.91201083935590976</v>
-      </c>
-      <c r="C36">
-        <v>1400</v>
-      </c>
-      <c r="D36">
-        <v>1000</v>
-      </c>
-      <c r="E36">
-        <v>88</v>
-      </c>
-      <c r="F36">
-        <v>372.6666666666664</v>
-      </c>
-      <c r="G36">
-        <v>372.6666666666664</v>
-      </c>
-      <c r="H36">
-        <v>54.722222222222193</v>
-      </c>
-      <c r="I36">
-        <v>4.5856927000131691</v>
-      </c>
-      <c r="J36">
-        <v>2.2400200003176E-2</v>
-      </c>
-      <c r="K36">
-        <v>4.6080929000163451</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A37">
-        <v>70000</v>
-      </c>
-      <c r="B37">
-        <v>0.63095734448019325</v>
-      </c>
-      <c r="C37">
-        <v>7000</v>
-      </c>
-      <c r="D37">
-        <v>1000</v>
-      </c>
-      <c r="E37">
-        <v>1</v>
-      </c>
-      <c r="F37">
-        <v>308.77777777777783</v>
-      </c>
-      <c r="G37">
-        <v>308.77777777777783</v>
-      </c>
-      <c r="H37">
-        <v>39.916666666666671</v>
-      </c>
-      <c r="I37">
-        <v>4.6082562000083271</v>
-      </c>
-      <c r="J37">
-        <v>2.7450800000224259E-2</v>
-      </c>
-      <c r="K37">
-        <v>4.6357070000085514</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>70000</v>
-      </c>
-      <c r="B38">
-        <v>0.63095734448019325</v>
-      </c>
-      <c r="C38">
-        <v>7000</v>
-      </c>
-      <c r="D38">
-        <v>1000</v>
-      </c>
-      <c r="E38">
-        <v>9</v>
-      </c>
-      <c r="F38">
-        <v>373.94444444444451</v>
-      </c>
-      <c r="G38">
-        <v>373.94444444444451</v>
-      </c>
-      <c r="H38">
-        <v>50.972222222222207</v>
-      </c>
-      <c r="I38">
-        <v>4.5601957000035327</v>
-      </c>
-      <c r="J38">
-        <v>2.4688099991180931E-2</v>
-      </c>
-      <c r="K38">
-        <v>4.5848837999947136</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A39">
-        <v>70000</v>
-      </c>
-      <c r="B39">
-        <v>0.63095734448019325</v>
-      </c>
-      <c r="C39">
-        <v>7000</v>
-      </c>
-      <c r="D39">
-        <v>1000</v>
-      </c>
-      <c r="E39">
-        <v>14</v>
-      </c>
-      <c r="F39">
-        <v>276.16666666666669</v>
-      </c>
-      <c r="G39">
-        <v>276.16666666666669</v>
-      </c>
-      <c r="H39">
-        <v>40.25</v>
-      </c>
-      <c r="I39">
-        <v>4.6824600999971153</v>
-      </c>
-      <c r="J39">
-        <v>2.5915599995641969E-2</v>
-      </c>
-      <c r="K39">
-        <v>4.7083756999927573</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <v>70000</v>
-      </c>
-      <c r="B40">
-        <v>0.63095734448019325</v>
-      </c>
-      <c r="C40">
-        <v>7000</v>
-      </c>
-      <c r="D40">
-        <v>1000</v>
-      </c>
-      <c r="E40">
-        <v>32</v>
-      </c>
-      <c r="F40">
-        <v>329.61111111111109</v>
-      </c>
-      <c r="G40">
-        <v>329.61111111111109</v>
-      </c>
-      <c r="H40">
-        <v>46.444444444444443</v>
-      </c>
-      <c r="I40">
-        <v>4.5942025999975158</v>
-      </c>
-      <c r="J40">
-        <v>2.5636299993493591E-2</v>
-      </c>
-      <c r="K40">
-        <v>4.6198388999910094</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <v>70000</v>
-      </c>
-      <c r="B41">
-        <v>0.63095734448019325</v>
-      </c>
-      <c r="C41">
-        <v>7000</v>
-      </c>
-      <c r="D41">
-        <v>1000</v>
-      </c>
-      <c r="E41">
-        <v>88</v>
-      </c>
-      <c r="F41">
-        <v>360.63888888888891</v>
-      </c>
-      <c r="G41">
-        <v>355.97222222222217</v>
-      </c>
-      <c r="H41">
-        <v>52.111111111111107</v>
-      </c>
-      <c r="I41">
-        <v>4.5572441000113031</v>
-      </c>
-      <c r="J41">
-        <v>4.8356900006183423E-2</v>
-      </c>
-      <c r="K41">
-        <v>4.6056010000174874</v>
+        <v>5.541402199989534</v>
       </c>
     </row>
   </sheetData>
@@ -1886,7 +2448,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.7109375" bestFit="1" customWidth="1"/>
@@ -1896,11 +2458,10 @@
     <col min="5" max="5" width="17.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="21.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -1922,221 +2483,111 @@
       <c r="G1" t="s">
         <v>15</v>
       </c>
-      <c r="H1" t="s">
-        <v>17</v>
-      </c>
-      <c r="I1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>750</v>
+        <v>500</v>
       </c>
       <c r="B2">
         <v>700</v>
       </c>
       <c r="C2">
-        <v>332.08888888888902</v>
+        <v>300.27777777777771</v>
       </c>
       <c r="D2">
-        <v>258.44444444444451</v>
-      </c>
-      <c r="E2">
-        <v>47.874379085681177</v>
+        <v>235</v>
+      </c>
+      <c r="E2" s="1">
+        <v>59.173046734780662</v>
       </c>
       <c r="F2">
-        <v>4.8425347799988234</v>
+        <v>4.3338623799994824</v>
       </c>
       <c r="G2">
         <v>5</v>
       </c>
-      <c r="H2">
-        <f>AVERAGE(E2:E5)</f>
-        <v>103.30250178292385</v>
-      </c>
-      <c r="I2">
-        <f>AVERAGE(C2:C5)</f>
-        <v>356.85</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>750</v>
+        <v>500</v>
       </c>
       <c r="B3">
         <v>1000</v>
       </c>
       <c r="C3">
-        <v>383.08888888888902</v>
+        <v>332.04444444444442</v>
       </c>
       <c r="D3">
-        <v>220.5</v>
-      </c>
-      <c r="E3">
-        <v>159.54875894685449</v>
+        <v>262.72222222222229</v>
+      </c>
+      <c r="E3" s="1">
+        <v>46.328397851974742</v>
       </c>
       <c r="F3">
-        <v>4.5621723399992344</v>
+        <v>4.5767704400059301</v>
       </c>
       <c r="G3">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>750</v>
+        <v>500</v>
       </c>
       <c r="B4">
         <v>1400</v>
       </c>
       <c r="C4">
-        <v>362.57777777777773</v>
+        <v>314.80555555555549</v>
       </c>
       <c r="D4">
-        <v>296.5555555555552</v>
-      </c>
-      <c r="E4">
-        <v>85.178383534820412</v>
+        <v>156.77777777777769</v>
+      </c>
+      <c r="E4" s="1">
+        <v>97.102748018990198</v>
       </c>
       <c r="F4">
-        <v>4.7143032000079987</v>
+        <v>5.1111768199974907</v>
       </c>
       <c r="G4">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>750</v>
+        <v>500</v>
       </c>
       <c r="B5">
         <v>7000</v>
       </c>
       <c r="C5">
-        <v>349.6444444444445</v>
+        <v>344.75555555555547</v>
       </c>
       <c r="D5">
-        <v>249.61111111111131</v>
-      </c>
-      <c r="E5">
-        <v>120.6084855643393</v>
+        <v>310.41666666666657</v>
+      </c>
+      <c r="E5" s="1">
+        <v>35.012637709585903</v>
       </c>
       <c r="F5">
-        <v>4.6432163999998011</v>
+        <v>5.0817025800002744</v>
       </c>
       <c r="G5">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>1000</v>
-      </c>
-      <c r="B6">
-        <v>700</v>
-      </c>
-      <c r="C6">
-        <v>336.20555555555552</v>
-      </c>
-      <c r="D6">
-        <v>248.83333333333329</v>
-      </c>
-      <c r="E6">
-        <v>75.012225341055327</v>
-      </c>
-      <c r="F6">
-        <v>4.6324892000004194</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-      <c r="H6">
-        <f>AVERAGE(E6:E9)</f>
-        <v>78.810599554929382</v>
-      </c>
-      <c r="I6">
-        <f>AVERAGE(C6:C9)</f>
-        <v>326.03611111111104</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>1000</v>
-      </c>
-      <c r="B7">
-        <v>1000</v>
-      </c>
-      <c r="C7">
-        <v>296.76111111111112</v>
-      </c>
-      <c r="D7">
-        <v>193</v>
-      </c>
-      <c r="E7">
-        <v>92.174853129162628</v>
-      </c>
-      <c r="F7">
-        <v>4.6758925800008004</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8">
-        <v>1000</v>
-      </c>
-      <c r="B8">
-        <v>1400</v>
-      </c>
-      <c r="C8">
-        <v>342.28333333333319</v>
-      </c>
-      <c r="D8">
-        <v>218</v>
-      </c>
-      <c r="E8">
-        <v>109.4932885930164</v>
-      </c>
-      <c r="F8">
-        <v>4.6371259399980769</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9">
-        <v>1000</v>
-      </c>
-      <c r="B9">
-        <v>7000</v>
-      </c>
-      <c r="C9">
-        <v>328.89444444444439</v>
-      </c>
-      <c r="D9">
-        <v>276.16666666666669</v>
-      </c>
-      <c r="E9">
-        <v>38.562031156483187</v>
-      </c>
-      <c r="F9">
-        <v>4.6308812800009038</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E6" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -2158,36 +2609,19 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>750</v>
+        <v>500</v>
       </c>
       <c r="B2">
-        <v>332.0888888888889</v>
+        <v>300.27777777777771</v>
       </c>
       <c r="C2">
-        <v>383.08888888888902</v>
+        <v>332.04444444444442</v>
       </c>
       <c r="D2">
-        <v>362.57777777777773</v>
+        <v>314.80555555555549</v>
       </c>
       <c r="E2">
-        <v>349.6444444444445</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>1000</v>
-      </c>
-      <c r="B3">
-        <v>336.20555555555552</v>
-      </c>
-      <c r="C3">
-        <v>296.76111111111112</v>
-      </c>
-      <c r="D3">
-        <v>342.28333333333319</v>
-      </c>
-      <c r="E3">
-        <v>328.89444444444439</v>
+        <v>344.75555555555547</v>
       </c>
     </row>
   </sheetData>
